--- a/jpcore-r4b/develop/StructureDefinition-jp-device.xlsx
+++ b/jpcore-r4b/develop/StructureDefinition-jp-device.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.0.0-dev-temp</t>
+    <t>2.0.0-dev</t>
   </si>
   <si>
     <t>Name</t>

--- a/jpcore-r4b/develop/StructureDefinition-jp-device.xlsx
+++ b/jpcore-r4b/develop/StructureDefinition-jp-device.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2634" uniqueCount="415">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2634" uniqueCount="422">
   <si>
     <t>Property</t>
   </si>
@@ -259,14 +259,14 @@
 </t>
   </si>
   <si>
-    <t>Item used in healthcare</t>
-  </si>
-  <si>
-    <t>A type of a manufactured item that is used in the provision of healthcare without being substantially changed through that activity. The device may be a medical or non-medical device.</t>
-  </si>
-  <si>
-    <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where(((id.exists() and ('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url)))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(uri) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}</t>
+    <t>ヘルスケアで使用されるアイテム / Item used in healthcare</t>
+  </si>
+  <si>
+    <t>その活動によって実質的に変更されることなく、ヘルスケアの提供に使用される製造されたアイテムの一種。このデバイスは、医療または非医療デバイスである場合があります。 / A type of a manufactured item that is used in the provision of healthcare without being substantially changed through that activity. The device may be a medical or non-medical device.</t>
+  </si>
+  <si>
+    <t>dom-2:リソースが別のリソースに含まれている場合、ネストされたリソースを含めてはなりません / If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
+dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where(((id.exists() and ('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url)))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(uri) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidもmeta.lastupdatedも持ってはならない。 / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が存在することが望ましい / A resource should have narrative for robust management {text.`div`.exists()}</t>
   </si>
   <si>
     <t>administrative.device</t>
@@ -285,13 +285,13 @@
 </t>
   </si>
   <si>
-    <t>Logical id of this artifact</t>
-  </si>
-  <si>
-    <t>The logical id of the resource, as used in the URL for the resource. Once assigned, this value never changes.</t>
-  </si>
-  <si>
-    <t>The only time that a resource does not have an id is when it is being submitted to the server using a create operation.</t>
+    <t>このアーティファクトの論理ID / Logical id of this artifact</t>
+  </si>
+  <si>
+    <t>リソースのURLで使用されるリソースの論理ID。割り当てられたら、この値は変更されません。 / The logical id of the resource, as used in the URL for the resource. Once assigned, this value never changes.</t>
+  </si>
+  <si>
+    <t>リソースにIDがないのは、IDが作成操作を使用してサーバーに送信されている場合です。 / The only time that a resource does not have an id is when it is being submitted to the server using a create operation.</t>
   </si>
   <si>
     <t>Resource.id</t>
@@ -304,26 +304,26 @@
 </t>
   </si>
   <si>
-    <t>Metadata about the resource</t>
-  </si>
-  <si>
-    <t>The metadata about the resource. This is content that is maintained by the infrastructure. Changes to the content might not always be associated with version changes to the resource.</t>
+    <t>リソースに関するMetadata / Metadata about the resource</t>
+  </si>
+  <si>
+    <t>リソースに関するMetadata。これは、インフラストラクチャによって維持されるコンテンツです。コンテンツの変更は、常にリソースのバージョンの変更に関連付けられているとは限りません。 / The metadata about the resource. This is content that is maintained by the infrastructure. Changes to the content might not always be associated with version changes to the resource.</t>
   </si>
   <si>
     <t>Resource.meta</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t xml:space="preserve">ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 </t>
   </si>
   <si>
     <t>Device.meta.id</t>
   </si>
   <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+    <t>エレメント相互参照のためのユニークID / Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>リソース内の要素の固有ID（内部参照用）。これは、スペースを含まない任意の文字列値である可能性があります。 / Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
   </si>
   <si>
     <t>Element.id</t>
@@ -343,13 +343,13 @@
 </t>
   </si>
   <si>
-    <t>Additional content defined by implementations</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
+    <t>実装によって定義される追加コンテンツ / Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>要素の基本的な定義に含まれない追加情報を表すために使用されることがあります。拡張機能の使用を安全かつ管理しやすくするために、定義および使用に適用される厳格なガバナンスのセットがあります。実装者は拡張機能を定義できますが、拡張機能の定義の一部として満たす必要のある要件のセットがあります。 / May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>どのようなアプリケーション、プロジェクト、または標準が拡張機能を使用しているかに関わらず、拡張機能の使用には決して汚名が付くわけではありません - それらを使用または定義する機関または管轄区域に関係なく。拡張機能の使用こそが、FHIR仕様を誰にとっても簡単なコアレベルで維持することを可能にします。 / There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
   </si>
   <si>
     <t xml:space="preserve">value:url}
@@ -365,23 +365,27 @@
     <t>Element.extension</t>
   </si>
   <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+    <t>ele-1:すべてのFHIR要素は、@valueまたはchildrenを持っている必要があります。 / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:extensionまたはvalue[x]のいずれかが必要です。両方ではありません。 / Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
     <t>Device.meta.versionId</t>
   </si>
   <si>
-    <t>Version specific identifier</t>
-  </si>
-  <si>
-    <t>The version specific identifier, as it appears in the version portion of the URL. This value changes when the resource is created, updated, or deleted.</t>
-  </si>
-  <si>
-    <t>The server assigns this value, and ignores what the client specifies, except in the case that the server is imposing version integrity on updates/deletes.</t>
+    <t>バージョン固有のidentifier (Baajon koyū no shikibetsu-shi) / Version specific identifier</t>
+  </si>
+  <si>
+    <t>URLのバージョン部分に表示されるバージョン固有のidentifier。この値は、リソースが作成、更新、または削除された場合に変更されます。 / The version specific identifier, as it appears in the version portion of the URL. This value changes when the resource is created, updated, or deleted.</t>
+  </si>
+  <si>
+    <t>サーバーがこの値を割り当て、クライアントが指定した値を無視する。ただし、サーバーが更新/削除時にバージョンの整合性を強制する場合を除く。 / The server assigns this value, and ignores what the client specifies, except in the case that the server is imposing version integrity on updates/deletes.</t>
   </si>
   <si>
     <t>Meta.versionId</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ele-1:すべてのFHIR要素は、@valueまたはchildrenを持っている必要があります。 / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+</t>
   </si>
   <si>
     <t>Device.meta.lastUpdated</t>
@@ -391,13 +395,13 @@
 </t>
   </si>
   <si>
-    <t>When the resource version last changed</t>
-  </si>
-  <si>
-    <t>When the resource last changed - e.g. when the version changed.</t>
-  </si>
-  <si>
-    <t>This value is always populated except when the resource is first being created. The server / resource manager sets this value; what a client provides is irrelevant. This is equivalent to the HTTP Last-Modified and SHOULD have the same value on a [read](http://hl7.org/fhir/R4B/http.html#read) interaction.</t>
+    <t>リソースのバージョンが最後に変更されたとき / When the resource version last changed</t>
+  </si>
+  <si>
+    <t>リソースが最後に変更されたとき - 例えば、バージョンが変更されたとき。 / When the resource last changed - e.g. when the version changed.</t>
+  </si>
+  <si>
+    <t>この値はリソースが初めて作成される場合を除いて常に設定されています。サーバー/リソースマネージャーがこの値を設定します。クライアントが提供する値は関係ありません。これはHTTP Last-Modifiedに相当し、[read](http://hl7.org/fhir/R4B/http.html#read)のインタラクションで同じ値を持つべきです。 / This value is always populated except when the resource is first being created. The server / resource manager sets this value; what a client provides is irrelevant. This is equivalent to the HTTP Last-Modified and SHOULD have the same value on a [read](http://hl7.org/fhir/R4B/http.html#read) interaction.</t>
   </si>
   <si>
     <t>Meta.lastUpdated</t>
@@ -410,13 +414,14 @@
 </t>
   </si>
   <si>
-    <t>Identifies where the resource comes from</t>
-  </si>
-  <si>
-    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](http://hl7.org/fhir/R4B/provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
-  </si>
-  <si>
-    <t>In the provenance resource, this corresponds to Provenance.entity.what[x]. The exact use of the source (and the implied Provenance.entity.role) is left to implementer discretion. Only one nominated source is allowed; for additional provenance details, a full Provenance resource should be used. 
+    <t>リソースがどこから来たかを特定する / Identifies where the resource comes from</t>
+  </si>
+  <si>
+    <t>リソースのソースシステムを識別するURI。これにより、リソース内の情報のソースをトラックまたは区別するために使用できる最小限の[プロビナンス]（provenance.html＃）情報が提供されます。ソースは、別のFHIRサーバー、ドキュメント、メッセージ、データベースなどを識別できます。 / A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](http://hl7.org/fhir/R4B/provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
+  </si>
+  <si>
+    <t>プロバナンスのリソースにおいて、これはProvenance.entity.what[x]に対応します。ソースの正確な使用方法（および含意されるProvenance.entity.role）は実装者の判断に委ねられます。指定されたソースは1つだけです。追加のプロバナンスの詳細が必要な場合は、完全なプロバナンスリソースを使用するべきです。
+この要素は、正規のURLでホストされていないリソースの現在のマスターソースがどこにあるかを示すために使用できます。 / In the provenance resource, this corresponds to Provenance.entity.what[x]. The exact use of the source (and the implied Provenance.entity.role) is left to implementer discretion. Only one nominated source is allowed; for additional provenance details, a full Provenance resource should be used. 
 This element can be used to indicate where the current master source of a resource that has a canonical URL if the resource is no longer hosted at the canonical URL.</t>
   </si>
   <si>
@@ -430,13 +435,13 @@
 </t>
   </si>
   <si>
-    <t>Profiles this resource claims to conform to</t>
-  </si>
-  <si>
-    <t>A list of profiles (references to [StructureDefinition](http://hl7.org/fhir/R4B/structuredefinition.html#) resources) that this resource claims to conform to. The URL is a reference to [StructureDefinition.url](http://hl7.org/fhir/R4B/structuredefinition-definitions.html#StructureDefinition.url).</t>
-  </si>
-  <si>
-    <t>It is up to the server and/or other infrastructure of policy to determine whether/how these claims are verified and/or updated over time.  The list of profile URLs is a set.</t>
+    <t>このリソースが適合を主張するプロファイル / Profiles this resource claims to conform to</t>
+  </si>
+  <si>
+    <t>このリソースが準拠すると主張する [StructureDefinition](http://hl7.org/fhir/R4B/structuredefinition.html#) リソースに関するプロファイルのリストです。URL は [StructureDefinition.url](http://hl7.org/fhir/R4B/structuredefinition-definitions.html#StructureDefinition.url) への参照です。 / A list of profiles (references to [StructureDefinition](http://hl7.org/fhir/R4B/structuredefinition.html#) resources) that this resource claims to conform to. The URL is a reference to [StructureDefinition.url](http://hl7.org/fhir/R4B/structuredefinition-definitions.html#StructureDefinition.url).</t>
+  </si>
+  <si>
+    <t>これらの主張が時間の経過に伴って検証または更新される方法と、それらを決定するサーバーや他の基盤に任されます。プロファイルURLのリストは1セットです。 / It is up to the server and/or other infrastructure of policy to determine whether/how these claims are verified and/or updated over time.  The list of profile URLs is a set.</t>
   </si>
   <si>
     <t>Meta.profile</t>
@@ -449,13 +454,13 @@
 </t>
   </si>
   <si>
-    <t>Security Labels applied to this resource</t>
-  </si>
-  <si>
-    <t>Security labels applied to this resource. These tags connect specific resources to the overall security policy and infrastructure.</t>
-  </si>
-  <si>
-    <t>The security labels can be updated without changing the stated version of the resource. The list of security labels is a set. Uniqueness is based the system/code, and version and display are ignored.</t>
+    <t>このリソースに適用されたセキュリティラベル / Security Labels applied to this resource</t>
+  </si>
+  <si>
+    <t>このリソースにはセキュリティラベルが適用されています。これらのタグにより、特定のリソースが全体的なセキュリティポリシーやインフラストラクチャに関連付けられます。 / Security labels applied to this resource. These tags connect specific resources to the overall security policy and infrastructure.</t>
+  </si>
+  <si>
+    <t>セキュリティラベルは変更せずにリソースのバージョンを更新可能です。セキュリティラベルのリストはセットであり、一意性はシステム/コードに基づき、バージョンと表示は無視されます。 / The security labels can be updated without changing the stated version of the resource. The list of security labels is a set. Uniqueness is based the system/code, and version and display are ignored.</t>
   </si>
   <si>
     <t>extensible</t>
@@ -470,13 +475,13 @@
     <t>Device.meta.tag</t>
   </si>
   <si>
-    <t>Tags applied to this resource</t>
-  </si>
-  <si>
-    <t>Tags applied to this resource. Tags are intended to be used to identify and relate resources to process and workflow, and applications are not required to consider the tags when interpreting the meaning of a resource.</t>
-  </si>
-  <si>
-    <t>The tags can be updated without changing the stated version of the resource. The list of tags is a set. Uniqueness is based the system/code, and version and display are ignored.</t>
+    <t>このリソースに適用されたタグ / Tags applied to this resource</t>
+  </si>
+  <si>
+    <t>このリソースに適用されるタグです。タグは、リソースをプロセスやワークフローに識別し、関連付けるために使用することが意図されており、アプリケーションはリソースの意味を解釈する際にタグを考慮する必要はありません。 / Tags applied to this resource. Tags are intended to be used to identify and relate resources to process and workflow, and applications are not required to consider the tags when interpreting the meaning of a resource.</t>
+  </si>
+  <si>
+    <t>リソースの表示バージョンを変更することなく、タグを更新できます。タグのリストは集合です。ユニーク性はシステム/コードに基づき、バージョンと表示は無視されます。 / The tags can be updated without changing the stated version of the resource. The list of tags is a set. Uniqueness is based the system/code, and version and display are ignored.</t>
   </si>
   <si>
     <t>example</t>
@@ -491,13 +496,13 @@
     <t>Device.implicitRules</t>
   </si>
   <si>
-    <t>A set of rules under which this content was created</t>
-  </si>
-  <si>
-    <t>A reference to a set of rules that were followed when the resource was constructed, and which must be understood when processing the content. Often, this is a reference to an implementation guide that defines the special rules along with other profiles etc.</t>
-  </si>
-  <si>
-    <t>Asserting this rule set restricts the content to be only understood by a limited set of trading partners. This inherently limits the usefulness of the data in the long term. However, the existing health eco-system is highly fractured, and not yet ready to define, collect, and exchange data in a generally computable sense. Wherever possible, implementers and/or specification writers should avoid using this element. Often, when used, the URL is a reference to an implementation guide that defines these special rules as part of it's narrative along with other profiles, value sets, etc.</t>
+    <t>このコンテンツが作成されたルールのセット / A set of rules under which this content was created</t>
+  </si>
+  <si>
+    <t>リソースが構築されたときに従った一連のルールへの参照。コンテンツの処理時に理解する必要があります。多くの場合、これは他のプロファイルなどとともに特別なルールを定義する実装ガイドへの参照です。 / A reference to a set of rules that were followed when the resource was constructed, and which must be understood when processing the content. Often, this is a reference to an implementation guide that defines the special rules along with other profiles etc.</t>
+  </si>
+  <si>
+    <t>このルールセットを主張することは、コンテンツが限られた取引パートナーのセットによってのみ理解されることを制限します。これにより、本質的に長期的にデータの有用性が制限されます。ただし、既存の健康エコシステムは非常に破壊されており、一般的に計算可能な意味でデータを定義、収集、交換する準備ができていません。可能な限り、実装者や仕様ライターはこの要素の使用を避ける必要があります。多くの場合、使用する場合、URLは、これらの特別なルールを他のプロファイル、バリューセットなどとともに叙述(Narative)の一部として定義する実装ガイドへの参照です。 / Asserting this rule set restricts the content to be only understood by a limited set of trading partners. This inherently limits the usefulness of the data in the long term. However, the existing health eco-system is highly fractured, and not yet ready to define, collect, and exchange data in a generally computable sense. Wherever possible, implementers and/or specification writers should avoid using this element. Often, when used, the URL is a reference to an implementation guide that defines these special rules as part of it's narrative along with other profiles, value sets, etc.</t>
   </si>
   <si>
     <t>Resource.implicitRules</t>
@@ -510,19 +515,19 @@
 </t>
   </si>
   <si>
-    <t>Language of the resource content</t>
-  </si>
-  <si>
-    <t>The base language in which the resource is written.</t>
-  </si>
-  <si>
-    <t>Language is provided to support indexing and accessibility (typically, services such as text to speech use the language tag). The html language tag in the narrative applies  to the narrative. The language tag on the resource may be used to specify the language of other presentations generated from the data in the resource. Not all the content has to be in the base language. The Resource.language should not be assumed to apply to the narrative automatically. If a language is specified, it should it also be specified on the div element in the html (see rules in HTML5 for information about the relationship between xml:lang and the html lang attribute).</t>
+    <t>リソースコンテンツの言語 / Language of the resource content</t>
+  </si>
+  <si>
+    <t>リソースが書かれている基本言語。 / The base language in which the resource is written.</t>
+  </si>
+  <si>
+    <t>言語は、インデックス作成とアクセシビリティをサポートするために提供されます（通常、テキストから音声までのサービスなどのサービスが言語タグを使用します）。叙述(Narative)のHTML言語タグは、叙述(Narative)に適用されます。リソース上の言語タグを使用して、リソース内のデータから生成された他のプレゼンテーションの言語を指定できます。すべてのコンテンツが基本言語である必要はありません。リソース。言語は、叙述(Narative)に自動的に適用されると想定されるべきではありません。言語が指定されている場合、HTMLのDIV要素にも指定されている場合（XML：LangとHTML Lang属性の関係については、HTML5のルールを参照してください）。 / Language is provided to support indexing and accessibility (typically, services such as text to speech use the language tag). The html language tag in the narrative applies  to the narrative. The language tag on the resource may be used to specify the language of other presentations generated from the data in the resource. Not all the content has to be in the base language. The Resource.language should not be assumed to apply to the narrative automatically. If a language is specified, it should it also be specified on the div element in the html (see rules in HTML5 for information about the relationship between xml:lang and the html lang attribute).</t>
   </si>
   <si>
     <t>preferred</t>
   </si>
   <si>
-    <t>IETF language tag</t>
+    <t>IETF言語タグ / IETF language tag</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/languages|4.3.0</t>
@@ -542,13 +547,13 @@
 </t>
   </si>
   <si>
-    <t>Text summary of the resource, for human interpretation</t>
-  </si>
-  <si>
-    <t>A human-readable narrative that contains a summary of the resource and can be used to represent the content of the resource to a human. The narrative need not encode all the structured data, but is required to contain sufficient detail to make it "clinically safe" for a human to just read the narrative. Resource definitions may define what content should be represented in the narrative to ensure clinical safety.</t>
-  </si>
-  <si>
-    <t>Contained resources do not have narrative. Resources that are not contained SHOULD have a narrative. In some cases, a resource may only have text with little or no additional discrete data (as long as all minOccurs=1 elements are satisfied).  This may be necessary for data from legacy systems where information is captured as a "text blob" or where text is additionally entered raw or narrated and encoded information is added later.</t>
+    <t>人間の解釈のためのリソースのテキスト概要 / Text summary of the resource, for human interpretation</t>
+  </si>
+  <si>
+    <t>リソースの概要を含み、人間へのリソースの内容を表すために使用できる人間の読み取り可能な叙述(Narative)。叙述(Narative)はすべての構造化されたデータをエンコードする必要はありませんが、人間が叙述(Narative)を読むだけで「臨床的に安全」にするために十分な詳細を含める必要があります。リソースの定義は、臨床的安全を確保するために、叙述(Narative)で表現するコンテンツを定義する場合があります。 / A human-readable narrative that contains a summary of the resource and can be used to represent the content of the resource to a human. The narrative need not encode all the structured data, but is required to contain sufficient detail to make it "clinically safe" for a human to just read the narrative. Resource definitions may define what content should be represented in the narrative to ensure clinical safety.</t>
+  </si>
+  <si>
+    <t>含まれるリソースには叙述(Narative)がありません。含まれていないリソースには叙述(Narative)が必要です。場合によっては、リソースには、追加の個別のデータがほとんどまたはまったくないテキストのみがあります（すべてのMinoccur = 1要素が満たされている限り）。これは、情報がtext blob (バイナリー ラージ オブジェクト)としてキャプチャされるレガシーシステムからのデータ、またはテキストが生またはナレーションされ、エンコードされた情報が後で追加される場合に必要になる場合があります。 / Contained resources do not have narrative. Resources that are not contained SHOULD have a narrative. In some cases, a resource may only have text with little or no additional discrete data (as long as all minOccurs=1 elements are satisfied).  This may be necessary for data from legacy systems where information is captured as a "text blob" or where text is additionally entered raw or narrated and encoded information is added later.</t>
   </si>
   <si>
     <t>DomainResource.text</t>
@@ -568,19 +573,19 @@
 </t>
   </si>
   <si>
-    <t>Contained, inline Resources</t>
-  </si>
-  <si>
-    <t>These resources do not have an independent existence apart from the resource that contains them - they cannot be identified independently, and nor can they have their own independent transaction scope.</t>
-  </si>
-  <si>
-    <t>This should never be done when the content can be identified properly, as once identification is lost, it is extremely difficult (and context dependent) to restore it again. Contained resources may have profiles and tags In their meta elements, but SHALL NOT have security labels.</t>
+    <t>インラインリソースが含まれています / Contained, inline Resources</t>
+  </si>
+  <si>
+    <t>これらのリソースには、それらを含むリソースを除いて独立した存在はありません - 独立して特定することはできず、独自の独立したトランザクションスコープを持つこともできません。 / These resources do not have an independent existence apart from the resource that contains them - they cannot be identified independently, and nor can they have their own independent transaction scope.</t>
+  </si>
+  <si>
+    <t>識別が失われると、コンテンツを適切に識別できる場合は、これを行うべきではありません。含まれるリソースには、メタ要素にプロファイルとタグがある場合がありますが、セキュリティラベルはありません。 / This should never be done when the content can be identified properly, as once identification is lost, it is extremely difficult (and context dependent) to restore it again. Contained resources may have profiles and tags In their meta elements, but SHALL NOT have security labels.</t>
   </si>
   <si>
     <t>DomainResource.contained</t>
   </si>
   <si>
-    <t xml:space="preserve">dom-r4b:Containing new R4B resources within R4 resources may cause interoperability issues if instances are shared with R4 systems {($this is Citation or $this is Evidence or $this is EvidenceReport or $this is EvidenceVariable or $this is MedicinalProductDefinition or $this is PackagedProductDefinition or $this is AdministrableProductDefinition or $this is Ingredient or $this is ClinicalUseDefinition or $this is RegulatedAuthorization or $this is SubstanceDefinition or $this is SubscriptionStatus or $this is SubscriptionTopic) implies (%resource is Citation or %resource is Evidence or %resource is EvidenceReport or %resource is EvidenceVariable or %resource is MedicinalProductDefinition or %resource is PackagedProductDefinition or %resource is AdministrableProductDefinition or %resource is Ingredient or %resource is ClinicalUseDefinition or %resource is RegulatedAuthorization or %resource is SubstanceDefinition or %resource is SubscriptionStatus or %resource is SubscriptionTopic)}
+    <t xml:space="preserve">dom-r4b:R4リソース内に新しいR4Bリソースを含めると、インスタンスがR4システムと共有された場合に相互運用性の問題が発生する可能性があります / Containing new R4B resources within R4 resources may cause interoperability issues if instances are shared with R4 systems {($this is Citation or $this is Evidence or $this is EvidenceReport or $this is EvidenceVariable or $this is MedicinalProductDefinition or $this is PackagedProductDefinition or $this is AdministrableProductDefinition or $this is Ingredient or $this is ClinicalUseDefinition or $this is RegulatedAuthorization or $this is SubstanceDefinition or $this is SubscriptionStatus or $this is SubscriptionTopic) implies (%resource is Citation or %resource is Evidence or %resource is EvidenceReport or %resource is EvidenceVariable or %resource is MedicinalProductDefinition or %resource is PackagedProductDefinition or %resource is AdministrableProductDefinition or %resource is Ingredient or %resource is ClinicalUseDefinition or %resource is RegulatedAuthorization or %resource is SubstanceDefinition or %resource is SubscriptionStatus or %resource is SubscriptionTopic)}
 </t>
   </si>
   <si>
@@ -590,23 +595,34 @@
     <t>Device.extension</t>
   </si>
   <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+    <t>実装で定義された追加のコンテンツ / Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>リソースの基本的な定義の一部ではない追加情報を表すために使用できます。拡張機能を安全で管理しやすくするために、拡張機能の定義と使用に適用される厳格なガバナンスセットがあります。実装者は拡張機能を定義できますが、拡張機能の定義の一部として満たされる一連の要件があります。 / May be used to represent additional information that is not part of the basic definition of the resource. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>拡張機能を使用または定義する機関や管轄権に関係なく、アプリケーション、プロジェクト、または標準による拡張機能の使用に関連するスティグマはありません。拡張機能の使用は、FHIR仕様がすべての人にコアレベルのシンプルさを保持できるようにするものです。 / There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
   </si>
   <si>
     <t>DomainResource.extension</t>
   </si>
   <si>
+    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:両方ではなく、拡張または値[x]が必要です / Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+  </si>
+  <si>
     <t>Device.modifierExtension</t>
   </si>
   <si>
-    <t>Extensions that cannot be ignored</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the resource and that modifies the understanding of the element that contains it and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer is allowed to define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
+    <t>無視できない拡張機能 / Extensions that cannot be ignored</t>
+  </si>
+  <si>
+    <t>リソースの基本的な定義の一部ではなく、それを含む要素の理解および/または含有要素の子孫の理解を変更するために使用される場合があります。通常、修飾子要素は否定または資格を提供します。拡張機能を安全で管理しやすくするために、拡張機能の定義と使用に適用される厳格なガバナンスセットがあります。実装者は拡張機能を定義することが許可されていますが、拡張機能の定義の一部として満たされる一連の要件があります。アプリケーションの処理リソースは、修飾子拡張機能をチェックする必要があります。
+モディファイア拡張は、リソースまたはdomainResource上の要素の意味を変更してはなりません（修飾軸自体の意味を変更することはできません）。 / May be used to represent additional information that is not part of the basic definition of the resource and that modifies the understanding of the element that contains it and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer is allowed to define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
 Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
   </si>
   <si>
-    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4B/extensibility.html#modifierExtension).</t>
+    <t>修飾子拡張機能により、安全に無視できる大部分の拡張機能と明確に区別できるように、安全に無視できない拡張機能が可能になります。これにより、実装者が拡張の存在を禁止する必要性を排除することにより、相互運用性が促進されます。詳細については、[修飾子拡張の定義]（拡張性.html＃modifierextension）を参照してください。 / Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4B/extensibility.html#modifierExtension).</t>
   </si>
   <si>
     <t>DomainResource.modifierExtension</t>
@@ -619,13 +635,13 @@
 </t>
   </si>
   <si>
-    <t>Instance identifier</t>
-  </si>
-  <si>
-    <t>Unique instance identifiers assigned to a device by manufacturers other organizations or owners.</t>
-  </si>
-  <si>
-    <t>The barcode string from a barcode present on a device label or package may identify the instance, include names given to the device in local usage, or may identify the type of device. If the identifier identifies the type of device, Device.type element should be used.</t>
+    <t>インスタンスidentifier / Instance identifier</t>
+  </si>
+  <si>
+    <t>他の組織または所有者を製造業者によってデバイスに割り当てられた一意のインスタンスidentifier。 / Unique instance identifiers assigned to a device by manufacturers other organizations or owners.</t>
+  </si>
+  <si>
+    <t>デバイスラベルまたはパッケージに存在するバーコードのバーコード文字列には、インスタンスを識別したり、ローカル使用でデバイスに指定された名前を含めるか、デバイスのタイプを識別したりすることがあります。identifierがデバイスのタイプを識別する場合、device.type要素を使用する必要があります。 / The barcode string from a barcode present on a device label or package may identify the instance, include names given to the device in local usage, or may identify the type of device. If the identifier identifies the type of device, Device.type element should be used.</t>
   </si>
   <si>
     <t>.id</t>
@@ -644,10 +660,10 @@
 </t>
   </si>
   <si>
-    <t>The reference to the definition for the device</t>
-  </si>
-  <si>
-    <t>The reference to the definition for the device.</t>
+    <t>デバイスの定義への参照 / The reference to the definition for the device</t>
+  </si>
+  <si>
+    <t>デバイスの定義への参照。 / The reference to the definition for the device.</t>
   </si>
   <si>
     <t>Device.udiCarrier</t>
@@ -657,16 +673,16 @@
 </t>
   </si>
   <si>
-    <t>Unique Device Identifier (UDI) Barcode string</t>
-  </si>
-  <si>
-    <t>Unique device identifier (UDI) assigned to device label or package.  Note that the Device may include multiple udiCarriers as it either may include just the udiCarrier for the jurisdiction it is sold, or for multiple jurisdictions it could have been sold.</t>
-  </si>
-  <si>
-    <t>UDI may identify an unique instance of a device, or it may only identify the type of the device.  See [UDI mappings](http://hl7.org/fhir/R4B/device-mappings.html#udi) for a complete mapping of UDI parts to Device.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
+    <t>一意のデバイスidentifier（UDI）バーコード文字列 / Unique Device Identifier (UDI) Barcode string</t>
+  </si>
+  <si>
+    <t>デバイスラベルまたはパッケージに割り当てられた一意のデバイスidentifier（UDI）。デバイスには、販売されている管轄権のためのudicarrierのみが含まれているか、販売されていた可能性のある複数の管轄区域のために、複数のudicarriersが含まれる場合があることに注意してください。 / Unique device identifier (UDI) assigned to device label or package.  Note that the Device may include multiple udiCarriers as it either may include just the udiCarrier for the jurisdiction it is sold, or for multiple jurisdictions it could have been sold.</t>
+  </si>
+  <si>
+    <t>UDIは、デバイスの一意のインスタンスを識別するか、デバイスのタイプのみを識別する場合があります。UDI部品のデバイスへの完全なマッピングについては、[udiマッピング]（device-mappings.html＃udi）を参照してください。 / UDI may identify an unique instance of a device, or it may only identify the type of the device.  See [UDI mappings](http://hl7.org/fhir/R4B/device-mappings.html#udi) for a complete mapping of UDI parts to Device.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ele-1:空のParametersリソースでない限り、すべてのFHIR要素には@valueまたはchildrenが必要です / All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
 </t>
   </si>
   <si>
@@ -680,7 +696,16 @@
 </t>
   </si>
   <si>
+    <t>要素間参照のための一意のID / Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>リソース内の要素の一意のID（内部参照用）。これは、スペースを含まない文字列値である場合があります。 / Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
     <t>Device.udiCarrier.extension</t>
+  </si>
+  <si>
+    <t>要素の基本的な定義の一部ではない追加情報を表すために使用できます。拡張機能を安全で管理しやすくするために、拡張機能の定義と使用に適用される厳格なガバナンスセットがあります。実装者は拡張機能を定義できますが、拡張機能の定義の一部として満たされる一連の要件があります。 / May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
   </si>
   <si>
     <t>Device.udiCarrier.modifierExtension</t>
@@ -690,10 +715,11 @@
 user contentmodifiers</t>
   </si>
   <si>
-    <t>Extensions that cannot be ignored even if unrecognized</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element and that modifies the understanding of the element in which it is contained and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
+    <t>認識されていなくても無視できない拡張機能 / Extensions that cannot be ignored even if unrecognized</t>
+  </si>
+  <si>
+    <t>要素の基本的な定義の一部ではなく、それが含まれている要素の理解、および/または含まれる要素の子孫の理解を変更するために使用される場合があります。通常、修飾子要素は否定または資格を提供します。拡張機能を安全で管理しやすくするために、拡張機能の定義と使用に適用される厳格なガバナンスセットがあります。実装者は拡張機能を定義できますが、拡張機能の定義の一部として満たされる一連の要件があります。アプリケーションの処理リソースは、修飾子拡張機能をチェックする必要があります。
+モディファイア拡張は、リソースまたはdomainResource上の要素の意味を変更してはなりません（修飾軸自体の意味を変更することはできません）。 / May be used to represent additional information that is not part of the basic definition of the element and that modifies the understanding of the element in which it is contained and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
 Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
   </si>
   <si>
@@ -707,10 +733,10 @@
 </t>
   </si>
   <si>
-    <t>Mandatory fixed portion of UDI</t>
-  </si>
-  <si>
-    <t>The device identifier (DI) is a mandatory, fixed portion of a UDI that identifies the labeler and the specific version or model of a device.</t>
+    <t>UDIの必須の固定部分 / Mandatory fixed portion of UDI</t>
+  </si>
+  <si>
+    <t>デバイスidentifier（DI）は、デバイスのラベルと特定のバージョンまたはモデルを識別するUDIの必須の固定部分です。 / The device identifier (DI) is a mandatory, fixed portion of a UDI that identifies the labeler and the specific version or model of a device.</t>
   </si>
   <si>
     <t>Role.id.extension</t>
@@ -729,10 +755,18 @@
 </t>
   </si>
   <si>
-    <t>UDI Issuing Organization</t>
-  </si>
-  <si>
-    <t>Organization that is charged with issuing UDIs for devices.  For example, the US FDA issuers include :
+    <t>UDI発行組織 / UDI Issuing Organization</t>
+  </si>
+  <si>
+    <t>デバイスのUDIの発行を担当する組織。たとえば、米国のFDA発行者には次のものが含まれます。
+1）GS1：
+http://hl7.org/fhir/namingsystem/gs1-di、
+2）HIBCC：
+http://hl7.org/fhir/namingsystem/hibcc-di、
+3）血液容器用のICCBBA：
+http://hl7.org/fhir/namingsystem/iccbba-blood-di、
+4）他のデバイス用のICCBA：
+http://hl7.org/fhir/namingsystem/iccbba-other-di。 / Organization that is charged with issuing UDIs for devices.  For example, the US FDA issuers include :
 1) GS1: 
 http://hl7.org/fhir/NamingSystem/gs1-di, 
 2) HIBCC:
@@ -760,13 +794,13 @@
     <t>Device.udiCarrier.jurisdiction</t>
   </si>
   <si>
-    <t>Regional UDI authority</t>
-  </si>
-  <si>
-    <t>The identity of the authoritative source for UDI generation within a  jurisdiction.  All UDIs are globally unique within a single namespace with the appropriate repository uri as the system.  For example,  UDIs of devices managed in the U.S. by the FDA, the value is  http://hl7.org/fhir/NamingSystem/fda-udi.</t>
-  </si>
-  <si>
-    <t>Allows a recipient of a UDI to know which database will contain the UDI-associated metadata.</t>
+    <t>地域UDI当局 / Regional UDI authority</t>
+  </si>
+  <si>
+    <t>管轄内のUDI世代の権威ある情報源のアイデンティティ。すべてのUDIは、システムとして適切なリポジトリURIを備えた単一の名前空間内でグローバルにユニークです。たとえば、FDAによって米国で管理されているデバイスのUDISは、http://hl7.org/fhir/namingsystem/fda-udiです。 / The identity of the authoritative source for UDI generation within a  jurisdiction.  All UDIs are globally unique within a single namespace with the appropriate repository uri as the system.  For example,  UDIs of devices managed in the U.S. by the FDA, the value is  http://hl7.org/fhir/NamingSystem/fda-udi.</t>
+  </si>
+  <si>
+    <t>UDIの受信者が、どのデータベースがUDI関連Metadataを含むかを知ることができます。 / Allows a recipient of a UDI to know which database will contain the UDI-associated metadata.</t>
   </si>
   <si>
     <t>Role.scoper</t>
@@ -783,13 +817,13 @@
 </t>
   </si>
   <si>
-    <t>UDI Machine Readable Barcode String</t>
-  </si>
-  <si>
-    <t>The full UDI carrier of the Automatic Identification and Data Capture (AIDC) technology representation of the barcode string as printed on the packaging of the device - e.g., a barcode or RFID.   Because of limitations on character sets in XML and the need to round-trip JSON data through XML, AIDC Formats *SHALL* be base64 encoded.</t>
-  </si>
-  <si>
-    <t>The AIDC form of UDIs should be scanned or otherwise used for the identification of the device whenever possible to minimize errors in records resulting from manual transcriptions. If separate barcodes for DI and PI are present, concatenate the string with DI first and in order of human readable expression on label.</t>
+    <t>UDIマシン読み取り可能なバーコード文字列 / UDI Machine Readable Barcode String</t>
+  </si>
+  <si>
+    <t>デバイスのパッケージに印刷されたバーコード文字列の自動識別とデータキャプチャ（AIDC）テクノロジー表現の完全なUDIキャリア - 例えば、バーコードやRFID。XMLの文字セットの制限とXMLを介してJSONデータを往復する必要があるため、AIDC形式 *はBase64エンコードされます。 / The full UDI carrier of the Automatic Identification and Data Capture (AIDC) technology representation of the barcode string as printed on the packaging of the device - e.g., a barcode or RFID.   Because of limitations on character sets in XML and the need to round-trip JSON data through XML, AIDC Formats *SHALL* be base64 encoded.</t>
+  </si>
+  <si>
+    <t>UDIのAIDC形式は、手動の転写に起因するレコードのエラーを最小限に抑えるために、可能な限りデバイスの識別にスキャンまたは使用する必要があります。DIとPIの個別のバーコードが存在する場合、最初にDIと文字列を連結し、ラベル上の人間の読み取り可能な式の順に連結します。 / The AIDC form of UDIs should be scanned or otherwise used for the identification of the device whenever possible to minimize errors in records resulting from manual transcriptions. If separate barcodes for DI and PI are present, concatenate the string with DI first and in order of human readable expression on label.</t>
   </si>
   <si>
     <t>A unique device identifier (UDI) on a device label a form that uses automatic identification and data capture (AIDC) technology.</t>
@@ -802,13 +836,13 @@
 </t>
   </si>
   <si>
-    <t>UDI Human Readable Barcode String</t>
-  </si>
-  <si>
-    <t>The full UDI carrier as the human readable form (HRF) representation of the barcode string as printed on the packaging of the device.</t>
-  </si>
-  <si>
-    <t>If separate barcodes for DI and PI are present, concatenate the string with DI first and in order of human readable expression on label.</t>
+    <t>UDIヒューマンリーダブルバーコード文字列 / UDI Human Readable Barcode String</t>
+  </si>
+  <si>
+    <t>デバイスのパッケージに印刷されたバーコード文字列の人間の読み取り可能なフォーム（HRF）表現としての完全なUDIキャリア。 / The full UDI carrier as the human readable form (HRF) representation of the barcode string as printed on the packaging of the device.</t>
+  </si>
+  <si>
+    <t>DIとPIの個別のバーコードが存在する場合、最初にDIと文字列を連結し、ラベル上の人間の読み取り可能な式の順に連結します。 / If separate barcodes for DI and PI are present, concatenate the string with DI first and in order of human readable expression on label.</t>
   </si>
   <si>
     <t>A unique device identifier (UDI) on a device label in plain text</t>
@@ -817,19 +851,19 @@
     <t>Device.udiCarrier.entryType</t>
   </si>
   <si>
-    <t>barcode | rfid | manual +</t>
-  </si>
-  <si>
-    <t>A coded entry to indicate how the data was entered.</t>
-  </si>
-  <si>
-    <t>Supports a way to distinguish hand entered from machine read data.</t>
+    <t>バーコード|rfid |マニュアル + / barcode | rfid | manual +</t>
+  </si>
+  <si>
+    <t>データの入力方法を示すコード化されたエントリ。 / A coded entry to indicate how the data was entered.</t>
+  </si>
+  <si>
+    <t>入力された手をマシン読み取りデータと区別する方法をサポートします。 / Supports a way to distinguish hand entered from machine read data.</t>
   </si>
   <si>
     <t>required</t>
   </si>
   <si>
-    <t>Codes to identify how UDI data was entered.</t>
+    <t>UDIデータがどのように入力されたかを識別するコード。 / Codes to identify how UDI data was entered.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/udi-entry-type|4.3.0</t>
@@ -841,16 +875,16 @@
     <t>Device.status</t>
   </si>
   <si>
-    <t>active | inactive | entered-in-error | unknown</t>
-  </si>
-  <si>
-    <t>Status of the Device availability.</t>
-  </si>
-  <si>
-    <t>This element is labeled as a modifier because the status contains the codes inactive and entered-in-error that mark the device (record)as not currently valid.</t>
-  </si>
-  <si>
-    <t>The availability status of the device.</t>
+    <t>アクティブ|非アクティブ|エラー入力|わからない / active | inactive | entered-in-error | unknown</t>
+  </si>
+  <si>
+    <t>デバイスの可用性のステータス。 / Status of the Device availability.</t>
+  </si>
+  <si>
+    <t>この要素には、ステータスが非アクティブであり、デバイス（レコード）を現在有効ではないとマークするエラーに入力されたコードが含まれているため、修飾子としてラベル付けされています。 / This element is labeled as a modifier because the status contains the codes inactive and entered-in-error that mark the device (record)as not currently valid.</t>
+  </si>
+  <si>
+    <t>デバイスの可用性ステータス。 / The availability status of the device.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/device-status|4.3.0</t>
@@ -869,13 +903,13 @@
 </t>
   </si>
   <si>
-    <t>online | paused | standby | offline | not-ready | transduc-discon | hw-discon | off</t>
-  </si>
-  <si>
-    <t>Reason for the dtatus of the Device availability.</t>
-  </si>
-  <si>
-    <t>The availability status reason of the device.</t>
+    <t>オンライン|一時停止|スタンバイ|オフライン|準備ができていない|transduc-discon |hw-discon |オフ / online | paused | standby | offline | not-ready | transduc-discon | hw-discon | off</t>
+  </si>
+  <si>
+    <t>デバイスの可用性のステータスの理由。 / Reason for the dtatus of the Device availability.</t>
+  </si>
+  <si>
+    <t>デバイスの可用性ステータス理由。 / The availability status reason of the device.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/device-status-reason|4.3.0</t>
@@ -888,13 +922,13 @@
 </t>
   </si>
   <si>
-    <t>The distinct identification string</t>
-  </si>
-  <si>
-    <t>The distinct identification string as required by regulation for a human cell, tissue, or cellular and tissue-based product.</t>
-  </si>
-  <si>
-    <t>For example, this applies to devices in the United States regulated under *Code of Federal Regulation 21CFR§1271.290(c)*.</t>
+    <t>明確な識別文字列 / The distinct identification string</t>
+  </si>
+  <si>
+    <t>ヒト細胞、組織、または細胞および組織ベースの生成物の規制で要求される明確な識別文字列。 / The distinct identification string as required by regulation for a human cell, tissue, or cellular and tissue-based product.</t>
+  </si>
+  <si>
+    <t>たとえば、これは、連邦規制のコード21CFR§1271.290（c） *に基づいて規制されている米国のデバイスに適用されます。 / For example, this applies to devices in the United States regulated under *Code of Federal Regulation 21CFR§1271.290(c)*.</t>
   </si>
   <si>
     <t>.lotNumberText</t>
@@ -906,10 +940,10 @@
     <t>Device.manufacturer</t>
   </si>
   <si>
-    <t>Name of device manufacturer</t>
-  </si>
-  <si>
-    <t>A name of the manufacturer.</t>
+    <t>デバイスメーカーの名前 / Name of device manufacturer</t>
+  </si>
+  <si>
+    <t>メーカーの名前。 / A name of the manufacturer.</t>
   </si>
   <si>
     <t>.playedRole[typeCode=MANU].scoper.name</t>
@@ -922,10 +956,10 @@
 </t>
   </si>
   <si>
-    <t>Date when the device was made</t>
-  </si>
-  <si>
-    <t>The date and time when the device was manufactured.</t>
+    <t>デバイスが作成された日付 / Date when the device was made</t>
+  </si>
+  <si>
+    <t>デバイスが製造された日付と時刻。 / The date and time when the device was manufactured.</t>
   </si>
   <si>
     <t>.existenceTime.low</t>
@@ -937,10 +971,10 @@
     <t>Device.expirationDate</t>
   </si>
   <si>
-    <t>Date and time of expiry of this device (if applicable)</t>
-  </si>
-  <si>
-    <t>The date and time beyond which this device is no longer valid or should not be used (if applicable).</t>
+    <t>このデバイスの有効期限の日時（該当する場合） / Date and time of expiry of this device (if applicable)</t>
+  </si>
+  <si>
+    <t>このデバイスがもはや有効でないか、使用すべきではない日付と時刻（該当する場合）。 / The date and time beyond which this device is no longer valid or should not be used (if applicable).</t>
   </si>
   <si>
     <t>.expirationTime</t>
@@ -952,22 +986,22 @@
     <t>Device.lotNumber</t>
   </si>
   <si>
-    <t>Lot number of manufacture</t>
-  </si>
-  <si>
-    <t>Lot number assigned by the manufacturer.</t>
+    <t>多くの製造 / Lot number of manufacture</t>
+  </si>
+  <si>
+    <t>メーカーによって割り当てられたロット番号。 / Lot number assigned by the manufacturer.</t>
   </si>
   <si>
     <t>Device.serialNumber</t>
   </si>
   <si>
-    <t>Serial number assigned by the manufacturer</t>
-  </si>
-  <si>
-    <t>The serial number assigned by the organization when the device was manufactured.</t>
-  </si>
-  <si>
-    <t>Alphanumeric Maximum 20.</t>
+    <t>メーカーによって割り当てられたシリアル番号 / Serial number assigned by the manufacturer</t>
+  </si>
+  <si>
+    <t>デバイスが製造されたときに組織によって割り当てられたシリアル番号。 / The serial number assigned by the organization when the device was manufactured.</t>
+  </si>
+  <si>
+    <t>英数字最大20。 / Alphanumeric Maximum 20.</t>
   </si>
   <si>
     <t>.playedRole[typeCode=MANU].id</t>
@@ -976,10 +1010,10 @@
     <t>Device.deviceName</t>
   </si>
   <si>
-    <t>The name of the device as given by the manufacturer</t>
-  </si>
-  <si>
-    <t>This represents the manufacturer's name of the device as provided by the device, from a UDI label, or by a person describing the Device.  This typically would be used when a person provides the name(s) or when the device represents one of the names available from DeviceDefinition.</t>
+    <t>メーカーによって与えられたデバイスの名前 / The name of the device as given by the manufacturer</t>
+  </si>
+  <si>
+    <t>これは、デバイスによって提供されるデバイスのメーカーの名前、UDIラベル、またはデバイスを説明する人が表します。これは通常、人が名前を提供するとき、またはデバイスがDevicedefinitionから利用可能な名前の1つを表すときに使用されます。 / This represents the manufacturer's name of the device as provided by the device, from a UDI label, or by a person describing the Device.  This typically would be used when a person provides the name(s) or when the device represents one of the names available from DeviceDefinition.</t>
   </si>
   <si>
     <t>Device.deviceName.id</t>
@@ -998,23 +1032,24 @@
 </t>
   </si>
   <si>
-    <t>The name that identifies the device</t>
-  </si>
-  <si>
-    <t>The name that identifies the device.</t>
+    <t>デバイスを識別する名前 / The name that identifies the device</t>
+  </si>
+  <si>
+    <t>デバイスを識別する名前。 / The name that identifies the device.</t>
   </si>
   <si>
     <t>Device.deviceName.type</t>
   </si>
   <si>
-    <t>udi-label-name | user-friendly-name | patient-reported-name | manufacturer-name | model-name | other</t>
-  </si>
-  <si>
-    <t>The type of deviceName.
+    <t>udi-label-name |ユーザーフレンドリーな名前|患者報告名|メーカー名|モデル名|他の / udi-label-name | user-friendly-name | patient-reported-name | manufacturer-name | model-name | other</t>
+  </si>
+  <si>
+    <t>Devicenameのタイプ。
+udilabelname |userfriendlyname |patientReportedName |製造済みviceName |ModelName。 / The type of deviceName.
 UDILabelName | UserFriendlyName | PatientReportedName | ManufactureDeviceName | ModelName.</t>
   </si>
   <si>
-    <t>The type of name the device is referred by.</t>
+    <t>デバイスが紹介されている名前のタイプ。 / The type of name the device is referred by.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/device-nametype|4.3.0</t>
@@ -1026,10 +1061,10 @@
     <t>Device.modelNumber</t>
   </si>
   <si>
-    <t>The manufacturer's model number for the device</t>
-  </si>
-  <si>
-    <t>The manufacturer's model number for the device.</t>
+    <t>デバイスのメーカーモデル番号 / The manufacturer's model number for the device</t>
+  </si>
+  <si>
+    <t>デバイスのメーカーモデル番号。 / The manufacturer's model number for the device.</t>
   </si>
   <si>
     <t>.softwareName (included as part)</t>
@@ -1038,22 +1073,22 @@
     <t>Device.partNumber</t>
   </si>
   <si>
-    <t>The part number or catalog number of the device</t>
-  </si>
-  <si>
-    <t>The part number or catalog number of the device.</t>
+    <t>デバイスの部品番号またはカタログ番号 / The part number or catalog number of the device</t>
+  </si>
+  <si>
+    <t>デバイスの部品番号またはカタログ番号。 / The part number or catalog number of the device.</t>
   </si>
   <si>
     <t>Device.type</t>
   </si>
   <si>
-    <t>The kind or type of device</t>
-  </si>
-  <si>
-    <t>The kind or type of device.</t>
-  </si>
-  <si>
-    <t>Codes to identify medical devices.</t>
+    <t>デバイスの種類または種類 / The kind or type of device</t>
+  </si>
+  <si>
+    <t>デバイスの種類または種類。 / The kind or type of device.</t>
+  </si>
+  <si>
+    <t>医療機器を識別するコード。 / Codes to identify medical devices.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/device-type|4.3.0</t>
@@ -1062,10 +1097,10 @@
     <t>Device.specialization</t>
   </si>
   <si>
-    <t>The capabilities supported on a  device, the standards to which the device conforms for a particular purpose, and used for the communication</t>
-  </si>
-  <si>
-    <t>The capabilities supported on a  device, the standards to which the device conforms for a particular purpose, and used for the communication.</t>
+    <t>デバイスでサポートされている機能、デバイスが特定の目的に適合し、通信に使用される標準 / The capabilities supported on a  device, the standards to which the device conforms for a particular purpose, and used for the communication</t>
+  </si>
+  <si>
+    <t>デバイスでサポートされている機能、デバイスが特定の目的に適合する標準で、通信に使用されます。 / The capabilities supported on a  device, the standards to which the device conforms for a particular purpose, and used for the communication.</t>
   </si>
   <si>
     <t>Device.specialization.id</t>
@@ -1080,28 +1115,28 @@
     <t>Device.specialization.systemType</t>
   </si>
   <si>
-    <t>The standard that is used to operate and communicate</t>
-  </si>
-  <si>
-    <t>The standard that is used to operate and communicate.</t>
+    <t>運用と通信に使用される標準 / The standard that is used to operate and communicate</t>
+  </si>
+  <si>
+    <t>運用と通信に使用される標準。 / The standard that is used to operate and communicate.</t>
   </si>
   <si>
     <t>Device.specialization.version</t>
   </si>
   <si>
-    <t>The version of the standard that is used to operate and communicate</t>
-  </si>
-  <si>
-    <t>The version of the standard that is used to operate and communicate.</t>
+    <t>操作と通信に使用される標準のバージョン / The version of the standard that is used to operate and communicate</t>
+  </si>
+  <si>
+    <t>操作と通信に使用される標準のバージョン。 / The version of the standard that is used to operate and communicate.</t>
   </si>
   <si>
     <t>Device.version</t>
   </si>
   <si>
-    <t>The actual design of the device or software version running on the device</t>
-  </si>
-  <si>
-    <t>The actual design of the device or software version running on the device.</t>
+    <t>デバイスで実行されているデバイスまたはソフトウェアバージョンの実際の設計 / The actual design of the device or software version running on the device</t>
+  </si>
+  <si>
+    <t>デバイスで実行されているデバイスまたはソフトウェアバージョンの実際の設計。 / The actual design of the device or software version running on the device.</t>
   </si>
   <si>
     <t>Device.version.id</t>
@@ -1116,37 +1151,37 @@
     <t>Device.version.type</t>
   </si>
   <si>
-    <t>The type of the device version, e.g. manufacturer, approved, internal</t>
-  </si>
-  <si>
-    <t>The type of the device version, e.g. manufacturer, approved, internal.</t>
+    <t>デバイスバージョンの種類（例：メーカー、承認済み、内部） / The type of the device version, e.g. manufacturer, approved, internal</t>
+  </si>
+  <si>
+    <t>デバイスバージョンの種類（例：メーカー、承認済み、内部）。 / The type of the device version, e.g. manufacturer, approved, internal.</t>
   </si>
   <si>
     <t>Device.version.component</t>
   </si>
   <si>
-    <t>A single component of the device version</t>
-  </si>
-  <si>
-    <t>A single component of the device version.</t>
+    <t>デバイスバージョンの単一コンポーネント / A single component of the device version</t>
+  </si>
+  <si>
+    <t>デバイスバージョンの単一コンポーネント。 / A single component of the device version.</t>
   </si>
   <si>
     <t>Device.version.value</t>
   </si>
   <si>
-    <t>The version text</t>
-  </si>
-  <si>
-    <t>The version text.</t>
+    <t>バージョンテキスト / The version text</t>
+  </si>
+  <si>
+    <t>バージョンテキスト。 / The version text.</t>
   </si>
   <si>
     <t>Device.property</t>
   </si>
   <si>
-    <t>The actual configuration settings of a device as it actually operates, e.g., regulation status, time properties</t>
-  </si>
-  <si>
-    <t>The actual configuration settings of a device as it actually operates, e.g., regulation status, time properties.</t>
+    <t>デバイスが実際に動作するときの実際の構成設定、例えば規制ステータス、時間プロパティ / The actual configuration settings of a device as it actually operates, e.g., regulation status, time properties</t>
+  </si>
+  <si>
+    <t>デバイスが実際に動作するときの実際の構成設定、たとえば、規制ステータス、時間プロパティ。 / The actual configuration settings of a device as it actually operates, e.g., regulation status, time properties.</t>
   </si>
   <si>
     <t>Device.property.id</t>
@@ -1161,10 +1196,10 @@
     <t>Device.property.type</t>
   </si>
   <si>
-    <t>Code that specifies the property DeviceDefinitionPropetyCode (Extensible)</t>
-  </si>
-  <si>
-    <t>Code that specifies the property DeviceDefinitionPropetyCode (Extensible).</t>
+    <t>プロパティDevicedEfinitionPropetycode（拡張可能）を指定するコード / Code that specifies the property DeviceDefinitionPropetyCode (Extensible)</t>
+  </si>
+  <si>
+    <t>プロパティDevicedEfinitionPropetycode（拡張可能）を指定するコード。 / Code that specifies the property DeviceDefinitionPropetyCode (Extensible).</t>
   </si>
   <si>
     <t>Device.property.valueQuantity</t>
@@ -1174,19 +1209,19 @@
 </t>
   </si>
   <si>
-    <t>Property value as a quantity</t>
-  </si>
-  <si>
-    <t>Property value as a quantity.</t>
+    <t>数量としてのプロパティ値 / Property value as a quantity</t>
+  </si>
+  <si>
+    <t>数量としてのプロパティ値。 / Property value as a quantity.</t>
   </si>
   <si>
     <t>Device.property.valueCode</t>
   </si>
   <si>
-    <t>Property value as a code, e.g., NTP4 (synced to NTP)</t>
-  </si>
-  <si>
-    <t>Property value as a code, e.g., NTP4 (synced to NTP).</t>
+    <t>コードとしてのプロパティ値、例えばNTP4（NTPに同期） / Property value as a code, e.g., NTP4 (synced to NTP)</t>
+  </si>
+  <si>
+    <t>コードとしてのプロパティ値、例えばNTP4（NTPに同期）。 / Property value as a code, e.g., NTP4 (synced to NTP).</t>
   </si>
   <si>
     <t>Device.patient</t>
@@ -1196,13 +1231,13 @@
 </t>
   </si>
   <si>
-    <t>Patient to whom Device is affixed</t>
-  </si>
-  <si>
-    <t>Patient information, If the device is affixed to a person.</t>
-  </si>
-  <si>
-    <t>If the device is implanted in a patient, then need to associate the device to the patient.</t>
+    <t>デバイスが貼られている患者 / Patient to whom Device is affixed</t>
+  </si>
+  <si>
+    <t>患者情報、デバイスが人に貼られている場合。 / Patient information, If the device is affixed to a person.</t>
+  </si>
+  <si>
+    <t>デバイスが患者に埋め込まれている場合は、デバイスを患者に関連付ける必要があります。 / If the device is implanted in a patient, then need to associate the device to the patient.</t>
   </si>
   <si>
     <t>.playedRole[typeCode=USED].scoper.playedRole[typeCode=PAT]</t>
@@ -1218,10 +1253,10 @@
 </t>
   </si>
   <si>
-    <t>Organization responsible for device</t>
-  </si>
-  <si>
-    <t>An organization that is responsible for the provision and ongoing maintenance of the device.</t>
+    <t>デバイスを担当する組織 / Organization responsible for device</t>
+  </si>
+  <si>
+    <t>デバイスの提供と継続的なメンテナンスを担当する組織。 / An organization that is responsible for the provision and ongoing maintenance of the device.</t>
   </si>
   <si>
     <t>.playedRole[typeCode=OWN].scoper</t>
@@ -1237,13 +1272,13 @@
 </t>
   </si>
   <si>
-    <t>Details for human/organization for support</t>
-  </si>
-  <si>
-    <t>Contact details for an organization or a particular human that is responsible for the device.</t>
-  </si>
-  <si>
-    <t>used for troubleshooting etc.</t>
+    <t>サポートのための人間/組織の詳細 / Details for human/organization for support</t>
+  </si>
+  <si>
+    <t>デバイスに責任がある組織または特定の人間の連絡先の詳細。 / Contact details for an organization or a particular human that is responsible for the device.</t>
+  </si>
+  <si>
+    <t>トラブルシューティングなどに使用されます。 / used for troubleshooting etc.</t>
   </si>
   <si>
     <t>.scopedRole[typeCode=CON].player</t>
@@ -1256,13 +1291,13 @@
 </t>
   </si>
   <si>
-    <t>Where the device is found</t>
-  </si>
-  <si>
-    <t>The place where the device can be found.</t>
-  </si>
-  <si>
-    <t>Device.location can be used to track device location.</t>
+    <t>デバイスが見つかった場所 / Where the device is found</t>
+  </si>
+  <si>
+    <t>デバイスを見つけることができる場所。 / The place where the device can be found.</t>
+  </si>
+  <si>
+    <t>Device.Locationを使用して、デバイスの場所を追跡できます。 / Device.location can be used to track device location.</t>
   </si>
   <si>
     <t>.playedRole[typeCode=LOCE].scoper</t>
@@ -1274,13 +1309,13 @@
     <t>Device.url</t>
   </si>
   <si>
-    <t>Network address to contact device</t>
-  </si>
-  <si>
-    <t>A network address on which the device may be contacted directly.</t>
-  </si>
-  <si>
-    <t>If the device is running a FHIR server, the network address should  be the Base URL from which a conformance statement may be retrieved.</t>
+    <t>連絡先デバイスへのネットワークアドレス / Network address to contact device</t>
+  </si>
+  <si>
+    <t>デバイスに直接連絡できるネットワークアドレス。 / A network address on which the device may be contacted directly.</t>
+  </si>
+  <si>
+    <t>デバイスがFHIRサーバーを実行している場合、ネットワークアドレスは、適合ステートメントを取得できるベースURLである必要があります。 / If the device is running a FHIR server, the network address should  be the Base URL from which a conformance statement may be retrieved.</t>
   </si>
   <si>
     <t>.telecom</t>
@@ -1293,10 +1328,10 @@
 </t>
   </si>
   <si>
-    <t>Device notes and comments</t>
-  </si>
-  <si>
-    <t>Descriptive information, usage information or implantation information that is not captured in an existing element.</t>
+    <t>デバイスのメモとコメント / Device notes and comments</t>
+  </si>
+  <si>
+    <t>既存の要素でキャプチャされていない記述情報、使用情報、または移植情報。 / Descriptive information, usage information or implantation information that is not captured in an existing element.</t>
   </si>
   <si>
     <t>.text</t>
@@ -1305,10 +1340,10 @@
     <t>Device.safety</t>
   </si>
   <si>
-    <t>Safety Characteristics of Device</t>
-  </si>
-  <si>
-    <t>Provides additional safety characteristics about a medical device.  For example devices containing latex.</t>
+    <t>デバイスの安全特性 / Safety Characteristics of Device</t>
+  </si>
+  <si>
+    <t>医療機器に関する追加の安全特性を提供します。たとえば、ラテックスを含むデバイス。 / Provides additional safety characteristics about a medical device.  For example devices containing latex.</t>
   </si>
   <si>
     <t>Device.parent</t>
@@ -1318,10 +1353,10 @@
 </t>
   </si>
   <si>
-    <t>The device that this device is attached to or is part of</t>
-  </si>
-  <si>
-    <t>The device that this device is attached to or is part of.</t>
+    <t>このデバイスが接続されている、または一部であるデバイス / The device that this device is attached to or is part of</t>
+  </si>
+  <si>
+    <t>このデバイスが接続されている、または一部であるデバイス。 / The device that this device is attached to or is part of.</t>
   </si>
 </sst>
 </file>
@@ -1665,7 +1700,7 @@
     <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="36.078125" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="63.0703125" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="43.49609375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
@@ -2448,7 +2483,7 @@
         <v>76</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>97</v>
+        <v>119</v>
       </c>
       <c r="AK7" t="s" s="2">
         <v>76</v>
@@ -2462,10 +2497,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -2488,16 +2523,16 @@
         <v>86</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2547,7 +2582,7 @@
         <v>76</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>77</v>
@@ -2559,7 +2594,7 @@
         <v>76</v>
       </c>
       <c r="AJ8" t="s" s="2">
-        <v>97</v>
+        <v>119</v>
       </c>
       <c r="AK8" t="s" s="2">
         <v>76</v>
@@ -2573,10 +2608,10 @@
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -2599,16 +2634,16 @@
         <v>86</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="N9" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -2658,7 +2693,7 @@
         <v>76</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>77</v>
@@ -2670,7 +2705,7 @@
         <v>76</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>97</v>
+        <v>119</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>76</v>
@@ -2684,10 +2719,10 @@
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -2710,16 +2745,16 @@
         <v>86</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="N10" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
@@ -2769,7 +2804,7 @@
         <v>76</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>77</v>
@@ -2781,7 +2816,7 @@
         <v>76</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>97</v>
+        <v>119</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>76</v>
@@ -2795,10 +2830,10 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2821,16 +2856,16 @@
         <v>86</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="N11" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
@@ -2856,11 +2891,11 @@
         <v>76</v>
       </c>
       <c r="X11" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="Y11" s="2"/>
       <c r="Z11" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AA11" t="s" s="2">
         <v>76</v>
@@ -2878,7 +2913,7 @@
         <v>76</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>77</v>
@@ -2890,7 +2925,7 @@
         <v>76</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>97</v>
+        <v>119</v>
       </c>
       <c r="AK11" t="s" s="2">
         <v>76</v>
@@ -2904,10 +2939,10 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2930,16 +2965,16 @@
         <v>86</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="N12" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
@@ -2965,11 +3000,11 @@
         <v>76</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="Y12" s="2"/>
       <c r="Z12" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>76</v>
@@ -2987,7 +3022,7 @@
         <v>76</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>77</v>
@@ -2999,7 +3034,7 @@
         <v>76</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>97</v>
+        <v>119</v>
       </c>
       <c r="AK12" t="s" s="2">
         <v>76</v>
@@ -3013,10 +3048,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3039,16 +3074,16 @@
         <v>86</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3098,7 +3133,7 @@
         <v>76</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>77</v>
@@ -3124,10 +3159,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3150,16 +3185,16 @@
         <v>76</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -3185,13 +3220,13 @@
         <v>76</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>76</v>
@@ -3209,7 +3244,7 @@
         <v>76</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>77</v>
@@ -3235,14 +3270,14 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
@@ -3261,16 +3296,16 @@
         <v>76</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -3320,7 +3355,7 @@
         <v>76</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>77</v>
@@ -3335,7 +3370,7 @@
         <v>97</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="AL15" t="s" s="2">
         <v>76</v>
@@ -3346,14 +3381,14 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -3372,16 +3407,16 @@
         <v>76</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -3431,7 +3466,7 @@
         <v>76</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>77</v>
@@ -3443,10 +3478,10 @@
         <v>76</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AL16" t="s" s="2">
         <v>76</v>
@@ -3457,10 +3492,10 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3486,13 +3521,13 @@
         <v>105</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>106</v>
+        <v>185</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>108</v>
+        <v>187</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -3542,7 +3577,7 @@
         <v>76</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>77</v>
@@ -3554,10 +3589,10 @@
         <v>76</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>113</v>
+        <v>189</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AL17" t="s" s="2">
         <v>76</v>
@@ -3568,10 +3603,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3597,16 +3632,16 @@
         <v>105</v>
       </c>
       <c r="L18" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="M18" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="N18" t="s" s="2">
         <v>187</v>
       </c>
-      <c r="M18" t="s" s="2">
-        <v>188</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>108</v>
-      </c>
       <c r="O18" t="s" s="2">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>76</v>
@@ -3655,7 +3690,7 @@
         <v>76</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>77</v>
@@ -3667,10 +3702,10 @@
         <v>76</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>113</v>
+        <v>189</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AL18" t="s" s="2">
         <v>76</v>
@@ -3681,10 +3716,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3707,16 +3742,16 @@
         <v>76</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -3766,7 +3801,7 @@
         <v>76</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>77</v>
@@ -3781,21 +3816,21 @@
         <v>97</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>198</v>
+        <v>202</v>
       </c>
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3818,13 +3853,13 @@
         <v>76</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -3875,7 +3910,7 @@
         <v>76</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>77</v>
@@ -3901,10 +3936,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3927,16 +3962,16 @@
         <v>86</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -3986,7 +4021,7 @@
         <v>76</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>77</v>
@@ -3998,13 +4033,13 @@
         <v>76</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="AM21" t="s" s="2">
         <v>76</v>
@@ -4012,10 +4047,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4038,13 +4073,13 @@
         <v>76</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>99</v>
+        <v>216</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>100</v>
+        <v>217</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -4121,10 +4156,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4150,13 +4185,13 @@
         <v>105</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>106</v>
+        <v>185</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>107</v>
+        <v>219</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>108</v>
+        <v>187</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -4218,7 +4253,7 @@
         <v>76</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>113</v>
+        <v>189</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>102</v>
@@ -4232,14 +4267,14 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>213</v>
+        <v>220</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>213</v>
+        <v>220</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>214</v>
+        <v>221</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
@@ -4261,16 +4296,16 @@
         <v>105</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>216</v>
+        <v>223</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>108</v>
+        <v>187</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>76</v>
@@ -4319,7 +4354,7 @@
         <v>76</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>77</v>
@@ -4331,10 +4366,10 @@
         <v>76</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>113</v>
+        <v>189</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AL24" t="s" s="2">
         <v>76</v>
@@ -4345,14 +4380,14 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>218</v>
+        <v>225</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>218</v>
+        <v>225</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
@@ -4371,13 +4406,13 @@
         <v>86</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>220</v>
+        <v>227</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>221</v>
+        <v>228</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -4428,7 +4463,7 @@
         <v>76</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>218</v>
+        <v>225</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>77</v>
@@ -4443,25 +4478,25 @@
         <v>97</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>224</v>
+        <v>231</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
@@ -4480,13 +4515,13 @@
         <v>76</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -4537,7 +4572,7 @@
         <v>76</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>77</v>
@@ -4552,21 +4587,21 @@
         <v>97</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>229</v>
+        <v>236</v>
       </c>
       <c r="AL26" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>230</v>
+        <v>237</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4589,17 +4624,17 @@
         <v>76</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>232</v>
+        <v>239</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>233</v>
+        <v>240</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" t="s" s="2">
-        <v>234</v>
+        <v>241</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>76</v>
@@ -4648,7 +4683,7 @@
         <v>76</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>77</v>
@@ -4663,7 +4698,7 @@
         <v>97</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="AL27" t="s" s="2">
         <v>76</v>
@@ -4674,14 +4709,14 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
@@ -4700,16 +4735,16 @@
         <v>86</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>238</v>
+        <v>245</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>240</v>
+        <v>247</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -4759,7 +4794,7 @@
         <v>76</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>77</v>
@@ -4774,25 +4809,25 @@
         <v>97</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="AL28" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>242</v>
+        <v>249</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>244</v>
+        <v>251</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
@@ -4811,16 +4846,16 @@
         <v>86</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>245</v>
+        <v>252</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>246</v>
+        <v>253</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>247</v>
+        <v>254</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -4870,7 +4905,7 @@
         <v>76</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>77</v>
@@ -4885,21 +4920,21 @@
         <v>97</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="AL29" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>248</v>
+        <v>255</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>249</v>
+        <v>256</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>249</v>
+        <v>256</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4922,17 +4957,17 @@
         <v>76</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" t="s" s="2">
-        <v>252</v>
+        <v>259</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>76</v>
@@ -4957,13 +4992,13 @@
         <v>76</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>253</v>
+        <v>260</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>254</v>
+        <v>261</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>255</v>
+        <v>262</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>76</v>
@@ -4981,7 +5016,7 @@
         <v>76</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>249</v>
+        <v>256</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>77</v>
@@ -4996,7 +5031,7 @@
         <v>97</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="AL30" t="s" s="2">
         <v>76</v>
@@ -5007,10 +5042,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>257</v>
+        <v>264</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>257</v>
+        <v>264</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5033,16 +5068,16 @@
         <v>86</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>258</v>
+        <v>265</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>260</v>
+        <v>267</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5068,13 +5103,13 @@
         <v>76</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>253</v>
+        <v>260</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>261</v>
+        <v>268</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>262</v>
+        <v>269</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>76</v>
@@ -5092,7 +5127,7 @@
         <v>76</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>257</v>
+        <v>264</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>77</v>
@@ -5107,10 +5142,10 @@
         <v>97</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>263</v>
+        <v>270</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>264</v>
+        <v>271</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>76</v>
@@ -5118,10 +5153,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>265</v>
+        <v>272</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>265</v>
+        <v>272</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5144,13 +5179,13 @@
         <v>76</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>266</v>
+        <v>273</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>267</v>
+        <v>274</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>268</v>
+        <v>275</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -5177,13 +5212,13 @@
         <v>76</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>269</v>
+        <v>276</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>270</v>
+        <v>277</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>76</v>
@@ -5201,7 +5236,7 @@
         <v>76</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>265</v>
+        <v>272</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>77</v>
@@ -5219,7 +5254,7 @@
         <v>76</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>264</v>
+        <v>271</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>76</v>
@@ -5227,14 +5262,14 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>271</v>
+        <v>278</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>271</v>
+        <v>278</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>272</v>
+        <v>279</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
@@ -5253,16 +5288,16 @@
         <v>76</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>273</v>
+        <v>280</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>274</v>
+        <v>281</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>275</v>
+        <v>282</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -5312,7 +5347,7 @@
         <v>76</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>271</v>
+        <v>278</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>77</v>
@@ -5327,21 +5362,21 @@
         <v>97</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>276</v>
+        <v>283</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>277</v>
+        <v>284</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>278</v>
+        <v>285</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>278</v>
+        <v>285</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5364,13 +5399,13 @@
         <v>76</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>279</v>
+        <v>286</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>280</v>
+        <v>287</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -5421,7 +5456,7 @@
         <v>76</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>278</v>
+        <v>285</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>77</v>
@@ -5436,21 +5471,21 @@
         <v>97</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>281</v>
+        <v>288</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>282</v>
+        <v>289</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>282</v>
+        <v>289</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5473,13 +5508,13 @@
         <v>76</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>283</v>
+        <v>290</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>284</v>
+        <v>291</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>285</v>
+        <v>292</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -5530,7 +5565,7 @@
         <v>76</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>282</v>
+        <v>289</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>77</v>
@@ -5545,21 +5580,21 @@
         <v>97</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>286</v>
+        <v>293</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>287</v>
+        <v>294</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>288</v>
+        <v>295</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>288</v>
+        <v>295</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5582,13 +5617,13 @@
         <v>76</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>283</v>
+        <v>290</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>289</v>
+        <v>296</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>290</v>
+        <v>297</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -5639,7 +5674,7 @@
         <v>76</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>288</v>
+        <v>295</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>77</v>
@@ -5654,21 +5689,21 @@
         <v>97</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>291</v>
+        <v>298</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>292</v>
+        <v>299</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>293</v>
+        <v>300</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>293</v>
+        <v>300</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5691,13 +5726,13 @@
         <v>76</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>294</v>
+        <v>301</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>295</v>
+        <v>302</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -5748,7 +5783,7 @@
         <v>76</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>293</v>
+        <v>300</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>77</v>
@@ -5763,21 +5798,21 @@
         <v>97</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>276</v>
+        <v>283</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>277</v>
+        <v>284</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5800,16 +5835,16 @@
         <v>76</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>297</v>
+        <v>304</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>298</v>
+        <v>305</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>299</v>
+        <v>306</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -5859,7 +5894,7 @@
         <v>76</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>77</v>
@@ -5874,10 +5909,10 @@
         <v>97</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>300</v>
+        <v>307</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>76</v>
@@ -5885,10 +5920,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>301</v>
+        <v>308</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>301</v>
+        <v>308</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5911,13 +5946,13 @@
         <v>76</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>302</v>
+        <v>309</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>303</v>
+        <v>310</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -5968,7 +6003,7 @@
         <v>76</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>301</v>
+        <v>308</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>77</v>
@@ -5980,7 +6015,7 @@
         <v>76</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>76</v>
@@ -5994,10 +6029,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>304</v>
+        <v>311</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>304</v>
+        <v>311</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6020,13 +6055,13 @@
         <v>76</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>99</v>
+        <v>216</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>100</v>
+        <v>217</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6103,10 +6138,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>305</v>
+        <v>312</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>305</v>
+        <v>312</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6132,13 +6167,13 @@
         <v>105</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>106</v>
+        <v>185</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>107</v>
+        <v>219</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>108</v>
+        <v>187</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -6200,7 +6235,7 @@
         <v>76</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>113</v>
+        <v>189</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>102</v>
@@ -6214,14 +6249,14 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>306</v>
+        <v>313</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>306</v>
+        <v>313</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>214</v>
+        <v>221</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -6243,16 +6278,16 @@
         <v>105</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>216</v>
+        <v>223</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>108</v>
+        <v>187</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>76</v>
@@ -6301,7 +6336,7 @@
         <v>76</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>77</v>
@@ -6313,10 +6348,10 @@
         <v>76</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>113</v>
+        <v>189</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AL42" t="s" s="2">
         <v>76</v>
@@ -6327,14 +6362,14 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>307</v>
+        <v>314</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>307</v>
+        <v>314</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>308</v>
+        <v>315</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -6353,13 +6388,13 @@
         <v>76</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>309</v>
+        <v>316</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>310</v>
+        <v>317</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -6410,7 +6445,7 @@
         <v>76</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>307</v>
+        <v>314</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>85</v>
@@ -6436,10 +6471,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>311</v>
+        <v>318</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>311</v>
+        <v>318</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6462,13 +6497,13 @@
         <v>76</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>312</v>
+        <v>319</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>313</v>
+        <v>320</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -6495,13 +6530,13 @@
         <v>76</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>253</v>
+        <v>260</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>314</v>
+        <v>321</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>315</v>
+        <v>322</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>76</v>
@@ -6519,7 +6554,7 @@
         <v>76</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>311</v>
+        <v>318</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>85</v>
@@ -6534,10 +6569,10 @@
         <v>97</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>316</v>
+        <v>323</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>76</v>
@@ -6545,10 +6580,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>317</v>
+        <v>324</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>317</v>
+        <v>324</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6571,13 +6606,13 @@
         <v>76</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>318</v>
+        <v>325</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>319</v>
+        <v>326</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -6628,7 +6663,7 @@
         <v>76</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>317</v>
+        <v>324</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>77</v>
@@ -6643,10 +6678,10 @@
         <v>97</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>76</v>
@@ -6654,10 +6689,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6680,16 +6715,16 @@
         <v>76</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>322</v>
+        <v>329</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>323</v>
+        <v>330</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>299</v>
+        <v>306</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -6739,7 +6774,7 @@
         <v>76</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>77</v>
@@ -6754,10 +6789,10 @@
         <v>97</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>300</v>
+        <v>307</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>76</v>
@@ -6765,10 +6800,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>324</v>
+        <v>331</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>324</v>
+        <v>331</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6791,13 +6826,13 @@
         <v>76</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>266</v>
+        <v>273</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>325</v>
+        <v>332</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>326</v>
+        <v>333</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -6824,13 +6859,13 @@
         <v>76</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>327</v>
+        <v>334</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>328</v>
+        <v>335</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>76</v>
@@ -6848,7 +6883,7 @@
         <v>76</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>324</v>
+        <v>331</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>77</v>
@@ -6874,10 +6909,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>329</v>
+        <v>336</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>329</v>
+        <v>336</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6900,13 +6935,13 @@
         <v>76</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>330</v>
+        <v>337</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>331</v>
+        <v>338</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -6957,7 +6992,7 @@
         <v>76</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>329</v>
+        <v>336</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>77</v>
@@ -6969,7 +7004,7 @@
         <v>76</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>76</v>
@@ -6983,10 +7018,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>332</v>
+        <v>339</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>332</v>
+        <v>339</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7009,13 +7044,13 @@
         <v>76</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>99</v>
+        <v>216</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>100</v>
+        <v>217</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -7092,10 +7127,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>333</v>
+        <v>340</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>333</v>
+        <v>340</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7121,13 +7156,13 @@
         <v>105</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>106</v>
+        <v>185</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>107</v>
+        <v>219</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>108</v>
+        <v>187</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -7189,7 +7224,7 @@
         <v>76</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>113</v>
+        <v>189</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>102</v>
@@ -7203,14 +7238,14 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>334</v>
+        <v>341</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>334</v>
+        <v>341</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>214</v>
+        <v>221</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
@@ -7232,16 +7267,16 @@
         <v>105</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>216</v>
+        <v>223</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>108</v>
+        <v>187</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>76</v>
@@ -7290,7 +7325,7 @@
         <v>76</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>77</v>
@@ -7302,10 +7337,10 @@
         <v>76</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>113</v>
+        <v>189</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AL51" t="s" s="2">
         <v>76</v>
@@ -7316,14 +7351,14 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>335</v>
+        <v>342</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>335</v>
+        <v>342</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>308</v>
+        <v>315</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
@@ -7342,13 +7377,13 @@
         <v>76</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>266</v>
+        <v>273</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>336</v>
+        <v>343</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>337</v>
+        <v>344</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -7399,7 +7434,7 @@
         <v>76</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>335</v>
+        <v>342</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>85</v>
@@ -7425,10 +7460,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>338</v>
+        <v>345</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>338</v>
+        <v>345</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7451,13 +7486,13 @@
         <v>76</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>339</v>
+        <v>346</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>340</v>
+        <v>347</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -7508,7 +7543,7 @@
         <v>76</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>338</v>
+        <v>345</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>77</v>
@@ -7526,7 +7561,7 @@
         <v>76</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>76</v>
@@ -7534,10 +7569,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>341</v>
+        <v>348</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>341</v>
+        <v>348</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7560,13 +7595,13 @@
         <v>76</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>342</v>
+        <v>349</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>343</v>
+        <v>350</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -7617,7 +7652,7 @@
         <v>76</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>341</v>
+        <v>348</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>77</v>
@@ -7629,7 +7664,7 @@
         <v>76</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="AK54" t="s" s="2">
         <v>76</v>
@@ -7643,10 +7678,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>344</v>
+        <v>351</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>344</v>
+        <v>351</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7669,13 +7704,13 @@
         <v>76</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>99</v>
+        <v>216</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>100</v>
+        <v>217</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -7752,10 +7787,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>345</v>
+        <v>352</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>345</v>
+        <v>352</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7781,13 +7816,13 @@
         <v>105</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>106</v>
+        <v>185</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>107</v>
+        <v>219</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>108</v>
+        <v>187</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -7849,7 +7884,7 @@
         <v>76</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>113</v>
+        <v>189</v>
       </c>
       <c r="AK56" t="s" s="2">
         <v>102</v>
@@ -7863,14 +7898,14 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>346</v>
+        <v>353</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>346</v>
+        <v>353</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>214</v>
+        <v>221</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
@@ -7892,16 +7927,16 @@
         <v>105</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>216</v>
+        <v>223</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>108</v>
+        <v>187</v>
       </c>
       <c r="O57" t="s" s="2">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>76</v>
@@ -7950,7 +7985,7 @@
         <v>76</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>77</v>
@@ -7962,10 +7997,10 @@
         <v>76</v>
       </c>
       <c r="AJ57" t="s" s="2">
-        <v>113</v>
+        <v>189</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AL57" t="s" s="2">
         <v>76</v>
@@ -7976,14 +8011,14 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>347</v>
+        <v>354</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>347</v>
+        <v>354</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
-        <v>308</v>
+        <v>315</v>
       </c>
       <c r="E58" s="2"/>
       <c r="F58" t="s" s="2">
@@ -8002,13 +8037,13 @@
         <v>76</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>266</v>
+        <v>273</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>348</v>
+        <v>355</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>349</v>
+        <v>356</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -8059,7 +8094,7 @@
         <v>76</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>347</v>
+        <v>354</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>77</v>
@@ -8085,10 +8120,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>350</v>
+        <v>357</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>350</v>
+        <v>357</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8111,13 +8146,13 @@
         <v>76</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>351</v>
+        <v>358</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>352</v>
+        <v>359</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -8168,7 +8203,7 @@
         <v>76</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>350</v>
+        <v>357</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>77</v>
@@ -8186,7 +8221,7 @@
         <v>76</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="AM59" t="s" s="2">
         <v>76</v>
@@ -8194,10 +8229,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>353</v>
+        <v>360</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>353</v>
+        <v>360</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8220,13 +8255,13 @@
         <v>76</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>354</v>
+        <v>361</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>355</v>
+        <v>362</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -8277,7 +8312,7 @@
         <v>76</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>353</v>
+        <v>360</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>85</v>
@@ -8303,10 +8338,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>356</v>
+        <v>363</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>356</v>
+        <v>363</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8329,13 +8364,13 @@
         <v>76</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>357</v>
+        <v>364</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>358</v>
+        <v>365</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -8386,7 +8421,7 @@
         <v>76</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>356</v>
+        <v>363</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>77</v>
@@ -8398,7 +8433,7 @@
         <v>76</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="AK61" t="s" s="2">
         <v>76</v>
@@ -8412,10 +8447,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>359</v>
+        <v>366</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>359</v>
+        <v>366</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8438,13 +8473,13 @@
         <v>76</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>99</v>
+        <v>216</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>100</v>
+        <v>217</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -8521,10 +8556,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>360</v>
+        <v>367</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>360</v>
+        <v>367</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8550,13 +8585,13 @@
         <v>105</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>106</v>
+        <v>185</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>107</v>
+        <v>219</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>108</v>
+        <v>187</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -8618,7 +8653,7 @@
         <v>76</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>113</v>
+        <v>189</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>102</v>
@@ -8632,14 +8667,14 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>361</v>
+        <v>368</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>361</v>
+        <v>368</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>214</v>
+        <v>221</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
@@ -8661,16 +8696,16 @@
         <v>105</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>216</v>
+        <v>223</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>108</v>
+        <v>187</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>76</v>
@@ -8719,7 +8754,7 @@
         <v>76</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>77</v>
@@ -8731,10 +8766,10 @@
         <v>76</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>113</v>
+        <v>189</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AL64" t="s" s="2">
         <v>76</v>
@@ -8745,10 +8780,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>362</v>
+        <v>369</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>362</v>
+        <v>369</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -8771,13 +8806,13 @@
         <v>76</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>266</v>
+        <v>273</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>363</v>
+        <v>370</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>364</v>
+        <v>371</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -8828,7 +8863,7 @@
         <v>76</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>362</v>
+        <v>369</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>85</v>
@@ -8854,10 +8889,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>365</v>
+        <v>372</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>365</v>
+        <v>372</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -8880,13 +8915,13 @@
         <v>76</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>366</v>
+        <v>373</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>367</v>
+        <v>374</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>368</v>
+        <v>375</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -8937,7 +8972,7 @@
         <v>76</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>365</v>
+        <v>372</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>77</v>
@@ -8963,10 +8998,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>369</v>
+        <v>376</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>369</v>
+        <v>376</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -8989,13 +9024,13 @@
         <v>76</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>266</v>
+        <v>273</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>370</v>
+        <v>377</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -9046,7 +9081,7 @@
         <v>76</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>369</v>
+        <v>376</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>77</v>
@@ -9072,10 +9107,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9098,17 +9133,17 @@
         <v>76</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>373</v>
+        <v>380</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>374</v>
+        <v>381</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>375</v>
+        <v>382</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" t="s" s="2">
-        <v>376</v>
+        <v>383</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>76</v>
@@ -9157,7 +9192,7 @@
         <v>76</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>372</v>
+        <v>379</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>77</v>
@@ -9172,10 +9207,10 @@
         <v>97</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>377</v>
+        <v>384</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>378</v>
+        <v>385</v>
       </c>
       <c r="AM68" t="s" s="2">
         <v>76</v>
@@ -9183,10 +9218,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>379</v>
+        <v>386</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>379</v>
+        <v>386</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9209,13 +9244,13 @@
         <v>76</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>380</v>
+        <v>387</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>381</v>
+        <v>388</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>382</v>
+        <v>389</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -9266,7 +9301,7 @@
         <v>76</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>379</v>
+        <v>386</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>77</v>
@@ -9281,10 +9316,10 @@
         <v>97</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>383</v>
+        <v>390</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>384</v>
+        <v>391</v>
       </c>
       <c r="AM69" t="s" s="2">
         <v>76</v>
@@ -9292,10 +9327,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>385</v>
+        <v>392</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>385</v>
+        <v>392</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9318,16 +9353,16 @@
         <v>76</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>386</v>
+        <v>393</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>387</v>
+        <v>394</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>388</v>
+        <v>395</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>389</v>
+        <v>396</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -9377,7 +9412,7 @@
         <v>76</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>385</v>
+        <v>392</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>77</v>
@@ -9392,10 +9427,10 @@
         <v>97</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>390</v>
+        <v>397</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>384</v>
+        <v>391</v>
       </c>
       <c r="AM70" t="s" s="2">
         <v>76</v>
@@ -9403,10 +9438,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>391</v>
+        <v>398</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>391</v>
+        <v>398</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -9429,17 +9464,17 @@
         <v>76</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>392</v>
+        <v>399</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>393</v>
+        <v>400</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>394</v>
+        <v>401</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" t="s" s="2">
-        <v>395</v>
+        <v>402</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>76</v>
@@ -9488,7 +9523,7 @@
         <v>76</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>391</v>
+        <v>398</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>77</v>
@@ -9503,10 +9538,10 @@
         <v>97</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>396</v>
+        <v>403</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>397</v>
+        <v>404</v>
       </c>
       <c r="AM71" t="s" s="2">
         <v>76</v>
@@ -9514,10 +9549,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>398</v>
+        <v>405</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>398</v>
+        <v>405</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -9540,16 +9575,16 @@
         <v>76</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>399</v>
+        <v>406</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>400</v>
+        <v>407</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>401</v>
+        <v>408</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -9599,7 +9634,7 @@
         <v>76</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>398</v>
+        <v>405</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>77</v>
@@ -9614,10 +9649,10 @@
         <v>97</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>402</v>
+        <v>409</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>397</v>
+        <v>404</v>
       </c>
       <c r="AM72" t="s" s="2">
         <v>76</v>
@@ -9625,10 +9660,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>403</v>
+        <v>410</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>403</v>
+        <v>410</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -9651,13 +9686,13 @@
         <v>76</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>404</v>
+        <v>411</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>405</v>
+        <v>412</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>406</v>
+        <v>413</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -9708,7 +9743,7 @@
         <v>76</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>403</v>
+        <v>410</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>77</v>
@@ -9723,7 +9758,7 @@
         <v>97</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>407</v>
+        <v>414</v>
       </c>
       <c r="AL73" t="s" s="2">
         <v>76</v>
@@ -9734,10 +9769,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>408</v>
+        <v>415</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>408</v>
+        <v>415</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -9760,13 +9795,13 @@
         <v>86</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>266</v>
+        <v>273</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>409</v>
+        <v>416</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>410</v>
+        <v>417</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -9817,7 +9852,7 @@
         <v>76</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>408</v>
+        <v>415</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>77</v>
@@ -9832,7 +9867,7 @@
         <v>97</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="AL74" t="s" s="2">
         <v>76</v>
@@ -9843,10 +9878,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>411</v>
+        <v>418</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>411</v>
+        <v>418</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -9869,13 +9904,13 @@
         <v>76</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>412</v>
+        <v>419</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>413</v>
+        <v>420</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>414</v>
+        <v>421</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -9926,7 +9961,7 @@
         <v>76</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>411</v>
+        <v>418</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>77</v>
